--- a/docs/sprint2/audit/audit-Pinchuk.xlsx
+++ b/docs/sprint2/audit/audit-Pinchuk.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -59,16 +48,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
@@ -77,10 +66,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -448,16 +437,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,20 +468,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Критерій</t>
+          <t>Критерій (моя оцінка)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Опис дефекту (пункт чек-листа, цитата)</t>
+          <t>Пункт чек-листа</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Пропозиція виправлення</t>
+          <t>Що знайдено (запис під час перевірки)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Пропозиція (чернетка)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Результат зведення</t>
         </is>
@@ -520,15 +515,20 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 4, 5: «обов'язковість полів позначено у формі зірочкою» — які поля обов'язкові, не визначено; не описано реакцію на вже зареєстровану адресу email і на пароль, що не відповідає правилам.</t>
+          <t>п. 1, 4, 5</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>«…Обов'язкові всі поля, крім «номер будинку» (потребує підтвердження замовником). Якщо адреса email уже зареєстрована, система показує «A customer with this email address already exists.», обліковий запис не створюється; якщо пароль не відповідає правилам — повідомлення за GUI-50, обліковий запис не створюється».</t>
+          <t>«обов'язковість полів позначено у формі зірочкою» — а які саме поля обов'язкові, у тексті вимоги не сказано. Що робить система, якщо email уже зареєстрований? Що, якщо пароль не відповідає правилам? Ні те, ні інше не описано.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Перелічити обов'язкові поля прямо у F-10. Додати: email уже є в системі → повідомлення, обліковий запис не створюється; пароль не за правилами → помилка за GUI-50, обліковий запис не створюється.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Прийнято, № 5 реєстру</t>
         </is>
@@ -542,7 +542,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>F-100</t>
+          <t>F-20</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -552,22 +552,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Простежуваність</t>
+          <t>Однозначність</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>п. 2: «Обмеження на кількість одиниць у рядку визначає вимога BL-25» — вимоги BL-25 у специфікації немає, зв'язок не простежується.</t>
+          <t>п. 1, 4</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>«…Кількість одиниць у рядку — від 1 до 99 включно (BL-10, BL-20, BL-40)».</t>
+          <t>«перенаправляє користувача на відповідну сторінку» — яку саме? Для тест-кейсу входу немає одного очікуваного результату.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 17 реєстру</t>
+          <t>Після входу — сторінка кабінету /account; якщо вхід був на кроці «Sign in» оформлення — повернення на «Billing Address».</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 1 реєстру</t>
         </is>
       </c>
     </row>
@@ -579,7 +584,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>F-110</t>
+          <t>F-30</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -589,22 +594,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Однозначність</t>
+          <t>Здійсненність</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>п. 5: крок «Billing Address» (платіжна адреса) описано як «підтверджує адресу доставки»; термін «адреса доставки» у 1.3 відсутній, billing і shipping address — різні поняття.</t>
+          <t>єдиний пункт</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Термін «Адреса доставки» додано до 1.3: «адреса, за якою доставляється замовлення; у версії 1.0 вводиться на кроці «Billing Address» і збігається з платіжною адресою». У F-110: «на кроці 3 «Billing Address» підтверджує адресу доставки (див. 1.3)…».</t>
+          <t>«гарантує його доставку до поштової скриньки … не довше ніж за 1 секунду незалежно від поштового провайдера» — система відповідає лише за відправлення, далі лист іде через чужі поштові сервери.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 4 реєстру</t>
+          <t>Система передає лист поштовому сервісу не пізніше ніж за 30 с (?) і показує повідомлення про надсилання; вказати строк дії посилання (24 год?).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 18 реєстру</t>
         </is>
       </c>
     </row>
@@ -616,7 +626,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>F-110</t>
+          <t>F-40</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -631,17 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>п. 2: F-110 «для замовлень від 2000 грн доставка безкоштовна» суперечить BL-60 «0.00 грн, якщо сума після знижки не менша за 1500 грн».</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>F-110: «…вартість доставки визначається за BL-60: 0 грн, якщо сума після знижок не менша за 1500 грн, інакше 120 грн» (поріг 1500 грн після знижки потребує підтвердження замовником).</t>
+          <t>F-40: «по 9 карток на сторінці». Перевірила GUI-20, бо він описує ту саму сітку, — там «по 12 карток на сторінці».</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 9 реєстру</t>
+          <t>Залишити 9 (так і в demo), GUI-20 виправити на 9.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 10 реєстру</t>
         </is>
       </c>
     </row>
@@ -653,7 +668,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>F-140</t>
+          <t>F-60</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -663,22 +678,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Повнота</t>
+          <t>Однозначність</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>п. 4, 5: «До звернення можна додати файл-вкладення» — допустимі формати і розмір не визначені; реакція на недопустимий файл і на повідомлення коротше 50 символів не описана.</t>
+          <t>п. 1, 4</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>«Вкладення необов'язкове: один файл .txt, .pdf, .jpg або .png розміром до 2 МБ (потребує підтвердження замовником); інакше під полем — «Invalid file», звернення не надсилається. Повідомлення коротше 50 символів — «Message must be minimal 50 characters», звернення не надсилається».</t>
+          <t>«знайти товари, назви яких схожі на введений запит» — «схожі» як? Входження підрядка, нечіткий пошук, помилки в написанні, синоніми? Неясно, які товари мають бути в результаті.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 6 реєстру</t>
+          <t>Пошук за входженням запиту в назву як підрядка без урахування регістру; якщо нічого не знайдено — окреме повідомлення.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 2 реєстру</t>
         </is>
       </c>
     </row>
@@ -690,7 +710,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>F-20</t>
+          <t>F-90</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -700,22 +720,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Однозначність</t>
+          <t>Тестопридатність</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 4 чек-листа: «Після успішного входу система перенаправляє користувача на відповідну сторінку» — «відповідна» не визначена; тест-кейс входу не має одного очікуваного результату.</t>
+          <t>практичний тест, слова-маркери</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>«Після успішного входу система перенаправляє користувача на сторінку особистого кабінету «My account» (/account); якщо вхід виконано на кроці «Sign in» оформлення замовлення — на крок «Billing Address»».</t>
+          <t>«миттєво і без помилок» — маркери з чек-листа, числа немає, «пройдено / не пройдено» не визначити.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 1 реєстру</t>
+          <t>Після «Add to cart» не пізніше ніж за 2 с з'являється повідомлення про додавання, лічильник кошика збільшується на кількість із «Quantity».</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 22 реєстру</t>
         </is>
       </c>
     </row>
@@ -727,7 +752,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>F-30</t>
+          <t>F-100</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -737,22 +762,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Здійсненність</t>
+          <t>Простежуваність</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>«гарантує його доставку до поштової скриньки … не довше ніж за 1 секунду незалежно від поштового провайдера» — доставка залежить від сторонніх поштових серверів, які продукт не контролює.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>«…система передає лист із посиланням поштовому сервісу не пізніше ніж за 30 с після надсилання форми і показує повідомлення про надсилання; посилання дійсне 24 год» (значення потребують підтвердження замовником).</t>
+          <t>«Обмеження на кількість одиниць у рядку визначає вимога BL-25» — у розділі 5 є BL-20 і BL-30, BL-25 немає.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 18 реєстру</t>
+          <t>Замінити посилання на BL-10, BL-20, BL-40 і прямо написати межі 1–99.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 17 реєстру</t>
         </is>
       </c>
     </row>
@@ -764,7 +794,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>F-110</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -774,22 +804,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Несуперечливість</t>
+          <t>Однозначність</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>п. 2: F-40 «по 9 карток на сторінці» суперечить GUI-20 «по 12 карток на сторінці».</t>
+          <t>п. 5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>GUI-20: «Картки каталогу розміщуються сіткою у три колонки по 9 карток на сторінці (три ряди)…» — узгоджено з F-40 і поточною версією demo.</t>
+          <t>Крок називається «Billing Address» (платіжна адреса), а в тексті — «підтверджує адресу доставки». Терміна «адреса доставки» в 1.3 немає. Одна це адреса чи дві різні?</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 10 реєстру</t>
+          <t>Додати в 1.3 термін «Адреса доставки» (у 1.0 збігається з платіжною, вводиться на кроці «Billing Address») і послатися на нього у F-110.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 4 реєстру</t>
         </is>
       </c>
     </row>
@@ -801,7 +836,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>F-60</t>
+          <t>F-110</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -811,22 +846,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Однозначність</t>
+          <t>Несуперечливість</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 4: «знайти товари, назви яких схожі на введений запит» — «схожі» допускає підрядок, нечіткий пошук, синоніми; невідомо, які товари мають потрапити у результат.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>«Поле пошуку знаходить товари, назва яких містить введений запит як підрядок без урахування регістру. Якщо збігів немає, система показує повідомлення «There are no products found.»».</t>
+          <t>«для замовлень від 2000 грн доставка безкоштовна» — у беклозі (US-09) було 1500 грн, тому перевірила BL-60: там 0 грн від 1500 грн після знижки. Ще й незрозуміло, «від 2000» — до знижок чи після.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 2 реєстру</t>
+          <t>Узгодити поріг між F-110 і BL-60 (питання замовнику).</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 9 реєстру; виправлення переписано при зведенні (посилання на BL-60, позначка «потребує підтвердження замовником»)</t>
         </is>
       </c>
     </row>
@@ -838,7 +878,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>F-90</t>
+          <t>F-140</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -848,22 +888,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність</t>
+          <t>Повнота</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>«додає товар у кошик … миттєво і без помилок» — «миттєво», «без помилок» не дають критерію «пройдено / не пройдено».</t>
+          <t>п. 4, 5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>«Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с з'являється повідомлення «Product added to shopping cart.», а лічильник кошика в шапці збільшується на цю кількість…».</t>
+          <t>«До звернення можна додати файл-вкладення» — які формати, який розмір? Що буде з недопустимим файлом? І яке повідомлення, якщо текст коротший за 50 символів?</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 22 реєстру</t>
+          <t>Вказати формати (.pdf, .jpg, .png, .txt?) і ліміт (2 МБ?); тексти повідомлень для недопустимого файлу і короткого повідомлення; звернення в обох випадках не надсилається.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 6 реєстру</t>
         </is>
       </c>
     </row>
@@ -890,15 +935,20 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 5: BL-30 «…не додає окремий рядок, а збільшує кількість у наявному рядку» повторює BL-20 і менш повна (без межі 99).</t>
+          <t>п. 1, 5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>BL-30 вилучено із записом у журналі змін; ID не перевикористовується; вимога — BL-20.</t>
+          <t>BL-30 каже те саме, що BL-20 (той самий sku → кількість у наявному рядку), тільки без межі 99. Дві вимоги на одне правило.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Вилучити BL-30, лишити BL-20.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Прийнято, № 16 реєстру</t>
         </is>
@@ -912,7 +962,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BL-70</t>
+          <t>BL-60</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -922,22 +972,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Повнота</t>
+          <t>Несуперечливість</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>п. 4, 5: не описано поведінку для коду, якого немає в довіднику, і для null-аргументів; «причина відмови» не має визначеного переліку значень — юніт-тест не може перевірити причину.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>«…Якщо код не знайдено — непридатний з причиною NOT_FOUND. Причини відмови: NOT_FOUND, INVALID_LENGTH, EXPIRED, ALREADY_USED, INVALID_VALUE; для придатного коду — порожня. Якщо будь-який аргумент null — IllegalArgumentException».</t>
+          <t>shippingFee: 0.00 від 1500 грн після знижки — а F-110 каже 2000. Той самий конфлікт, що в К-09, побачила вже з боку модуля.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 7 реєстру</t>
+          <t>Див. К-09.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Об'єднано з К-09 при зведенні → № 9 реєстру</t>
         </is>
       </c>
     </row>
@@ -949,30 +1004,77 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>BL-70</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>п. 4, 5</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>validate(): а якщо коду взагалі немає в довіднику? Що з null-аргументами? «Причина відмови» — який саме текст або код? Без переліку юніт-тест не перевірить причину.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Додати випадок «код не знайдено»; задати перелік причин відмови; для null — IllegalArgumentException.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 7 реєстру</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>К-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>BL-80</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Здійсненність</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>«перевіряє, що цей код не було використано у жодному іншому інтернет-магазині, зокрема сторонніх» — доступу до даних сторонніх магазинів немає; модуль за 2.3 — бібліотека без зовнішніх залежностей.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>«…Перед застосуванням одноразового коду система перевіряє, що його не використано в жодному замовленні «ШопЛайн»; використаний код відхиляється з причиною ALREADY_USED».</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>єдиний пункт</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>«перевіряє, що цей код не було використано у жодному іншому інтернет-магазині, зокрема сторонніх» — доступу до даних інших магазинів немає, а модуль за 2.3 без зовнішніх залежностей.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Перевіряти використання коду лише в замовленнях «ШопЛайн».</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Прийнято, № 20 реєстру</t>
         </is>
@@ -989,11 +1091,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1059,17 +1161,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Знайдено (всього)</t>
+          <t>Записів в аркуші</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Прийнято до реєстру</t>
+          <t>Прийнято до реєстру як окремий дефект</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1079,71 +1181,111 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Відхилено</t>
+          <t>Об'єднано з іншим записом при зведенні</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>— Однозначність</t>
+          <t>Відхилено на обговоренні</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>— Повнота</t>
+          <t>Перекласифіковано при зведенні</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>— Несуперечливість</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>2</v>
-      </c>
+          <t>Записи за критерієм (моя оцінка)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>— Простежуваність</t>
+          <t>— Однозначність</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>— Здійсненність</t>
+          <t>— Повнота</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>— Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>— Простежуваність</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>— Здійсненність</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>— Тестопридатність</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Примітка</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Колонки «Що знайдено» і «Пропозиція» — формулювання до зведення; узгоджений текст дефекту і виправлення — у requirements-defects.xlsx, аркуш «Реєстр». Розділи 1–2 пройдено за всіма шістьма чек-листами, дефектів не знайдено.</t>
+        </is>
       </c>
     </row>
   </sheetData>
